--- a/sheets/Libetee_増額シミュレーション_7月ベース.xlsx
+++ b/sheets/Libetee_増額シミュレーション_7月ベース.xlsx
@@ -18,11 +18,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.00&quot;%&quot;"/>
     <numFmt numFmtId="165" formatCode="¥#,##0"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="m/d(aaa)"/>
+    <numFmt numFmtId="166" formatCode="m/d(aaa)"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -139,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -228,34 +227,64 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1002,6 +1031,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1064,8 +1094,8 @@
       <c r="B5" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="6" t="n">
-        <v>0.6192807600396341</v>
+      <c r="C5" s="46" t="n">
+        <v>0.006192807600396341</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>19288</v>
@@ -1098,8 +1128,8 @@
       <c r="B6" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="11" t="n">
-        <v>0.7852441206543967</v>
+      <c r="C6" s="47" t="n">
+        <v>0.007852441206543968</v>
       </c>
       <c r="D6" s="12" t="n">
         <v>9532</v>
@@ -1132,8 +1162,8 @@
       <c r="B7" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="16" t="n">
-        <v>0.3378378378378378</v>
+      <c r="C7" s="48" t="n">
+        <v>0.003378378378378378</v>
       </c>
       <c r="D7" s="17" t="n">
         <v>27905</v>
@@ -1166,8 +1196,8 @@
       <c r="B8" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="C8" s="21" t="n">
-        <v>0.2904507629529755</v>
+      <c r="C8" s="49" t="n">
+        <v>0.002904507629529755</v>
       </c>
       <c r="D8" s="22" t="n">
         <v>17305</v>
@@ -1200,8 +1230,8 @@
       <c r="B9" s="25" t="n">
         <v>17</v>
       </c>
-      <c r="C9" s="26" t="n">
-        <v>0.355869271312969</v>
+      <c r="C9" s="50" t="n">
+        <v>0.00355869271312969</v>
       </c>
       <c r="D9" s="27" t="n">
         <v>11488</v>
@@ -1249,6 +1279,7 @@
         <v>66771315</v>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="31" t="inlineStr">
         <is>
@@ -1284,6 +1315,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
@@ -1437,6 +1469,7 @@
         <v>3474936</v>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="H8" t="inlineStr">
         <is>
@@ -1511,6 +1544,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -1554,7 +1588,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="36" t="n">
+      <c r="A4" s="51" t="n">
         <v>46235</v>
       </c>
       <c r="B4" s="15" t="inlineStr">
@@ -1582,7 +1616,7 @@
       <c r="H4" s="14" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="38" t="n">
+      <c r="A5" s="52" t="n">
         <v>46236</v>
       </c>
       <c r="B5" s="25" t="inlineStr">
@@ -1610,7 +1644,7 @@
       <c r="H5" s="24" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="38" t="n">
+      <c r="A6" s="52" t="n">
         <v>46237</v>
       </c>
       <c r="B6" s="25" t="inlineStr">
@@ -1638,7 +1672,7 @@
       <c r="H6" s="24" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="40" t="n">
+      <c r="A7" s="53" t="n">
         <v>46238</v>
       </c>
       <c r="B7" s="20" t="inlineStr">
@@ -1670,7 +1704,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="42" t="n">
+      <c r="A8" s="54" t="n">
         <v>46239</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -1702,7 +1736,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="40" t="n">
+      <c r="A9" s="53" t="n">
         <v>46240</v>
       </c>
       <c r="B9" s="20" t="inlineStr">
@@ -1730,7 +1764,7 @@
       <c r="H9" s="19" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="40" t="n">
+      <c r="A10" s="53" t="n">
         <v>46241</v>
       </c>
       <c r="B10" s="20" t="inlineStr">
@@ -1758,7 +1792,7 @@
       <c r="H10" s="19" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="40" t="n">
+      <c r="A11" s="53" t="n">
         <v>46242</v>
       </c>
       <c r="B11" s="20" t="inlineStr">
@@ -1786,7 +1820,7 @@
       <c r="H11" s="19" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="40" t="n">
+      <c r="A12" s="53" t="n">
         <v>46243</v>
       </c>
       <c r="B12" s="20" t="inlineStr">
@@ -1814,7 +1848,7 @@
       <c r="H12" s="19" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="42" t="n">
+      <c r="A13" s="54" t="n">
         <v>46244</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -1846,7 +1880,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="38" t="n">
+      <c r="A14" s="52" t="n">
         <v>46245</v>
       </c>
       <c r="B14" s="25" t="inlineStr">
@@ -1878,7 +1912,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="38" t="n">
+      <c r="A15" s="52" t="n">
         <v>46246</v>
       </c>
       <c r="B15" s="25" t="inlineStr">
@@ -1906,7 +1940,7 @@
       <c r="H15" s="24" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="38" t="n">
+      <c r="A16" s="52" t="n">
         <v>46247</v>
       </c>
       <c r="B16" s="25" t="inlineStr">
@@ -1934,7 +1968,7 @@
       <c r="H16" s="24" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="38" t="n">
+      <c r="A17" s="52" t="n">
         <v>46248</v>
       </c>
       <c r="B17" s="25" t="inlineStr">
@@ -1962,7 +1996,7 @@
       <c r="H17" s="24" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="44" t="n">
+      <c r="A18" s="55" t="n">
         <v>46249</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -1990,7 +2024,7 @@
       <c r="H18" s="9" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="38" t="n">
+      <c r="A19" s="52" t="n">
         <v>46250</v>
       </c>
       <c r="B19" s="25" t="inlineStr">
@@ -2018,7 +2052,7 @@
       <c r="H19" s="24" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="38" t="n">
+      <c r="A20" s="52" t="n">
         <v>46251</v>
       </c>
       <c r="B20" s="25" t="inlineStr">
@@ -2046,7 +2080,7 @@
       <c r="H20" s="24" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="38" t="n">
+      <c r="A21" s="52" t="n">
         <v>46252</v>
       </c>
       <c r="B21" s="25" t="inlineStr">
@@ -2074,7 +2108,7 @@
       <c r="H21" s="24" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="38" t="n">
+      <c r="A22" s="52" t="n">
         <v>46253</v>
       </c>
       <c r="B22" s="25" t="inlineStr">
@@ -2102,7 +2136,7 @@
       <c r="H22" s="24" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="44" t="n">
+      <c r="A23" s="55" t="n">
         <v>46254</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
@@ -2130,7 +2164,7 @@
       <c r="H23" s="9" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="38" t="n">
+      <c r="A24" s="52" t="n">
         <v>46255</v>
       </c>
       <c r="B24" s="25" t="inlineStr">
@@ -2158,7 +2192,7 @@
       <c r="H24" s="24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="38" t="n">
+      <c r="A25" s="52" t="n">
         <v>46256</v>
       </c>
       <c r="B25" s="25" t="inlineStr">
@@ -2186,7 +2220,7 @@
       <c r="H25" s="24" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="38" t="n">
+      <c r="A26" s="52" t="n">
         <v>46257</v>
       </c>
       <c r="B26" s="25" t="inlineStr">
@@ -2214,7 +2248,7 @@
       <c r="H26" s="24" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="40" t="n">
+      <c r="A27" s="53" t="n">
         <v>46258</v>
       </c>
       <c r="B27" s="20" t="inlineStr">
@@ -2246,7 +2280,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="42" t="n">
+      <c r="A28" s="54" t="n">
         <v>46259</v>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -2278,7 +2312,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="40" t="n">
+      <c r="A29" s="53" t="n">
         <v>46260</v>
       </c>
       <c r="B29" s="20" t="inlineStr">
@@ -2306,7 +2340,7 @@
       <c r="H29" s="19" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="38" t="n">
+      <c r="A30" s="52" t="n">
         <v>46261</v>
       </c>
       <c r="B30" s="25" t="inlineStr">
@@ -2338,7 +2372,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="38" t="n">
+      <c r="A31" s="52" t="n">
         <v>46262</v>
       </c>
       <c r="B31" s="25" t="inlineStr">
@@ -2366,7 +2400,7 @@
       <c r="H31" s="24" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="38" t="n">
+      <c r="A32" s="52" t="n">
         <v>46263</v>
       </c>
       <c r="B32" s="25" t="inlineStr">
@@ -2394,7 +2428,7 @@
       <c r="H32" s="24" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="44" t="n">
+      <c r="A33" s="55" t="n">
         <v>46264</v>
       </c>
       <c r="B33" s="10" t="inlineStr">
@@ -2422,7 +2456,7 @@
       <c r="H33" s="9" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="38" t="n">
+      <c r="A34" s="52" t="n">
         <v>46265</v>
       </c>
       <c r="B34" s="25" t="inlineStr">

--- a/sheets/Libetee_増額シミュレーション_7月ベース.xlsx
+++ b/sheets/Libetee_増額シミュレーション_7月ベース.xlsx
@@ -1588,8 +1588,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="n">
-        <v>46235</v>
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>8/1(土)</t>
+        </is>
       </c>
       <c r="B4" s="15" t="inlineStr">
         <is>
@@ -1616,8 +1618,10 @@
       <c r="H4" s="14" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="52" t="n">
-        <v>46236</v>
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>8/2(日)</t>
+        </is>
       </c>
       <c r="B5" s="25" t="inlineStr">
         <is>
@@ -1644,8 +1648,10 @@
       <c r="H5" s="24" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="52" t="n">
-        <v>46237</v>
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>8/3(月)</t>
+        </is>
       </c>
       <c r="B6" s="25" t="inlineStr">
         <is>
@@ -1672,8 +1678,10 @@
       <c r="H6" s="24" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="53" t="n">
-        <v>46238</v>
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>8/4(火)</t>
+        </is>
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
@@ -1704,8 +1712,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="54" t="n">
-        <v>46239</v>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>8/5(水)</t>
+        </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
@@ -1736,8 +1746,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="53" t="n">
-        <v>46240</v>
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>8/6(木)</t>
+        </is>
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
@@ -1764,8 +1776,10 @@
       <c r="H9" s="19" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="53" t="n">
-        <v>46241</v>
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>8/7(金)</t>
+        </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
@@ -1792,8 +1806,10 @@
       <c r="H10" s="19" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="53" t="n">
-        <v>46242</v>
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>8/8(土)</t>
+        </is>
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
@@ -1820,8 +1836,10 @@
       <c r="H11" s="19" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="53" t="n">
-        <v>46243</v>
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>8/9(日)</t>
+        </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
@@ -1848,8 +1866,10 @@
       <c r="H12" s="19" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="54" t="n">
-        <v>46244</v>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>8/10(月)</t>
+        </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -1880,8 +1900,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="52" t="n">
-        <v>46245</v>
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t>8/11(火)</t>
+        </is>
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
@@ -1912,8 +1934,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="52" t="n">
-        <v>46246</v>
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t>8/12(水)</t>
+        </is>
       </c>
       <c r="B15" s="25" t="inlineStr">
         <is>
@@ -1940,8 +1964,10 @@
       <c r="H15" s="24" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="52" t="n">
-        <v>46247</v>
+      <c r="A16" s="25" t="inlineStr">
+        <is>
+          <t>8/13(木)</t>
+        </is>
       </c>
       <c r="B16" s="25" t="inlineStr">
         <is>
@@ -1968,8 +1994,10 @@
       <c r="H16" s="24" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="52" t="n">
-        <v>46248</v>
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>8/14(金)</t>
+        </is>
       </c>
       <c r="B17" s="25" t="inlineStr">
         <is>
@@ -1996,8 +2024,10 @@
       <c r="H17" s="24" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="55" t="n">
-        <v>46249</v>
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>8/15(土)</t>
+        </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
@@ -2024,8 +2054,10 @@
       <c r="H18" s="9" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="52" t="n">
-        <v>46250</v>
+      <c r="A19" s="25" t="inlineStr">
+        <is>
+          <t>8/16(日)</t>
+        </is>
       </c>
       <c r="B19" s="25" t="inlineStr">
         <is>
@@ -2052,8 +2084,10 @@
       <c r="H19" s="24" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="52" t="n">
-        <v>46251</v>
+      <c r="A20" s="25" t="inlineStr">
+        <is>
+          <t>8/17(月)</t>
+        </is>
       </c>
       <c r="B20" s="25" t="inlineStr">
         <is>
@@ -2080,8 +2114,10 @@
       <c r="H20" s="24" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="52" t="n">
-        <v>46252</v>
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>8/18(火)</t>
+        </is>
       </c>
       <c r="B21" s="25" t="inlineStr">
         <is>
@@ -2108,8 +2144,10 @@
       <c r="H21" s="24" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="52" t="n">
-        <v>46253</v>
+      <c r="A22" s="25" t="inlineStr">
+        <is>
+          <t>8/19(水)</t>
+        </is>
       </c>
       <c r="B22" s="25" t="inlineStr">
         <is>
@@ -2136,8 +2174,10 @@
       <c r="H22" s="24" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="55" t="n">
-        <v>46254</v>
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>8/20(木)</t>
+        </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
@@ -2164,8 +2204,10 @@
       <c r="H23" s="9" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="52" t="n">
-        <v>46255</v>
+      <c r="A24" s="25" t="inlineStr">
+        <is>
+          <t>8/21(金)</t>
+        </is>
       </c>
       <c r="B24" s="25" t="inlineStr">
         <is>
@@ -2192,8 +2234,10 @@
       <c r="H24" s="24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="52" t="n">
-        <v>46256</v>
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>8/22(土)</t>
+        </is>
       </c>
       <c r="B25" s="25" t="inlineStr">
         <is>
@@ -2220,8 +2264,10 @@
       <c r="H25" s="24" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="52" t="n">
-        <v>46257</v>
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>8/23(日)</t>
+        </is>
       </c>
       <c r="B26" s="25" t="inlineStr">
         <is>
@@ -2248,8 +2294,10 @@
       <c r="H26" s="24" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="53" t="n">
-        <v>46258</v>
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>8/24(月)</t>
+        </is>
       </c>
       <c r="B27" s="20" t="inlineStr">
         <is>
@@ -2280,8 +2328,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="54" t="n">
-        <v>46259</v>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>8/25(火)</t>
+        </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
@@ -2312,8 +2362,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="53" t="n">
-        <v>46260</v>
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>8/26(水)</t>
+        </is>
       </c>
       <c r="B29" s="20" t="inlineStr">
         <is>
@@ -2340,8 +2392,10 @@
       <c r="H29" s="19" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="52" t="n">
-        <v>46261</v>
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>8/27(木)</t>
+        </is>
       </c>
       <c r="B30" s="25" t="inlineStr">
         <is>
@@ -2372,8 +2426,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="52" t="n">
-        <v>46262</v>
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>8/28(金)</t>
+        </is>
       </c>
       <c r="B31" s="25" t="inlineStr">
         <is>
@@ -2400,8 +2456,10 @@
       <c r="H31" s="24" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="52" t="n">
-        <v>46263</v>
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>8/29(土)</t>
+        </is>
       </c>
       <c r="B32" s="25" t="inlineStr">
         <is>
@@ -2428,8 +2486,10 @@
       <c r="H32" s="24" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="55" t="n">
-        <v>46264</v>
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>8/30(日)</t>
+        </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
@@ -2456,8 +2516,10 @@
       <c r="H33" s="9" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="52" t="n">
-        <v>46265</v>
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>8/31(月)</t>
+        </is>
       </c>
       <c r="B34" s="25" t="inlineStr">
         <is>
